--- a/Template_Bulk_Classes.xlsx
+++ b/Template_Bulk_Classes.xlsx
@@ -3,9 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Classes" sheetId="2" r:id="rId2"/>
-    <sheet name="Valid Types" sheetId="3" r:id="rId3"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -66,9 +65,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,176 +398,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
-  <cols>
-    <col min="1" max="1" width="105.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>📋 INSTRUCCIONES - Bulk Upload de Classes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>COLUMNAS REQUERIDAS (obligatorias):</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">  • Title        → Nombre de la clase</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">  • Date         → Fecha en formato YYYY-MM-DD (ej: 2026-04-01). NO usar formato corto como 4/1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">  • Start Time   → Hora de inicio en formato HH:MM (ej: 14:00). NO usar AM/PM</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">  • End Time     → Hora de fin en formato HH:MM (ej: 15:00). NO usar AM/PM</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>COLUMNAS OPCIONALES:</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">  • Type         → Tipo de clase. Valores permitidos: REGULAR, WORKSHOP, WEBINAR, QA, MASTERCLASS</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">                    Si se deja vacío, se usará REGULAR por defecto</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v xml:space="preserve">  • Meet Link    → URL de la reunión (Google Meet, Zoom, etc.)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">  • Capacity     → Número máximo de estudiantes. Escribir 'Unlimited' o dejar vacío para sin límite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">  • Description  → Descripción de la clase</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v xml:space="preserve">  • Materials Links → URLs de materiales (PDFs, docs, videos, etc.)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v xml:space="preserve">                      ✅ Para UN solo material: poner la URL directamente</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v xml:space="preserve">                      ✅ Para VARIOS materiales: separar las URLs con coma</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v xml:space="preserve">                      Ejemplo: https://link1.com/doc, https://link2.com/pdf, https://link3.com/video</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v xml:space="preserve">                      El estudiante verá un modal donde puede elegir cuál abrir</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>⚠️  REGLAS IMPORTANTES:</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">  1. NO se permiten fechas pasadas</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v xml:space="preserve">  2. Las fechas DEBEN estar en formato YYYY-MM-DD para evitar problemas</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v xml:space="preserve">  3. Las horas DEBEN estar en formato 24h HH:MM (ej: 09:00, 14:30, 18:00)</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v xml:space="preserve">  4. Para que Excel NO cambie el formato de fecha/hora, seleccionar las columnas Date/Start Time/End Time</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v xml:space="preserve">     y cambiar el formato de celda a 'Texto' ANTES de escribir los datos</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v xml:space="preserve">  5. Type debe ser EXACTAMENTE uno de: REGULAR, WORKSHOP, WEBINAR, QA, MASTERCLASS</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>💡 TIP: Completar los datos en la hoja 'Classes' →</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A29"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="42.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
-    <col min="9" max="9" width="85.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="70.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,152 +437,152 @@
         <v>Description</v>
       </c>
       <c r="I1" t="str">
-        <v>Materials Links</v>
+        <v>Materials Link</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Job Interview Practice</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="D2" s="1" t="str">
-        <v>15:00</v>
+        <v>Business English Basics</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="C2" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>10:00</v>
       </c>
       <c r="E2" t="str">
-        <v>QA</v>
+        <v>REGULAR</v>
       </c>
       <c r="F2" t="str">
         <v>https://meet.google.com/abc-defg-hij</v>
       </c>
-      <c r="G2">
-        <v>5</v>
+      <c r="G2" t="str">
+        <v>15</v>
       </c>
       <c r="H2" t="str">
-        <v>Discussing the best job application strategies</v>
+        <v>Introduction to business vocabulary and professional email writing.</v>
       </c>
       <c r="I2" t="str">
-        <v>https://docs.google.com/document/d/interview-guide</v>
+        <v>https://drive.google.com/file/d/business-basics-slides</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sales Roleplay</v>
-      </c>
-      <c r="B3" s="1" t="str">
-        <v>2026-04-02</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <v>11:00</v>
-      </c>
-      <c r="D3" s="1" t="str">
-        <v>12:00</v>
+        <v>IELTS Speaking Workshop</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="C3" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="D3" t="str">
+        <v>15:30</v>
       </c>
       <c r="E3" t="str">
-        <v>MASTERCLASS</v>
+        <v>WORKSHOP</v>
       </c>
       <c r="F3" t="str">
         <v>https://meet.google.com/xyz-uvwx-yz</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
         <v>10</v>
       </c>
       <c r="H3" t="str">
-        <v>Sales role-play with detailed feedback on grammar and pronunciation</v>
+        <v>Practice IELTS speaking Part 2 &amp; 3 with live feedback.</v>
       </c>
       <c r="I3" t="str">
-        <v>https://drive.google.com/file/d/sales-script, https://drive.google.com/file/d/roleplay-tips</v>
+        <v>https://drive.google.com/file/d/ielts-handout, https://drive.google.com/file/d/practice-topics, https://www.loom.com/share/ielts-tips-video</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mindset &amp; Conversation</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <v>2026-04-03</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <v>15:00</v>
+        <v>Grammar Q&amp;A Session</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="D4" t="str">
+        <v>19:00</v>
       </c>
       <c r="E4" t="str">
-        <v>WORKSHOP</v>
+        <v>QA</v>
       </c>
       <c r="F4" t="str">
-        <v>https://meet.google.com/klm-nopq-rst</v>
+        <v>https://zoom.us/j/1234567890</v>
       </c>
       <c r="G4" t="str">
-        <v>Unlimited</v>
+        <v>20</v>
       </c>
       <c r="H4" t="str">
-        <v>Group session focused on English debate practice</v>
+        <v>Open session to ask grammar questions. Bring your doubts!</v>
       </c>
       <c r="I4" t="str">
-        <v>https://example.com/debate-guide.pdf, https://example.com/vocabulary-list.pdf, https://youtu.be/example-video</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Grammar Fundamentals</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <v>2026-04-04</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <v>10:30</v>
+        <v>Sales Roleplay Masterclass</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="D5" t="str">
+        <v>11:30</v>
       </c>
       <c r="E5" t="str">
-        <v>REGULAR</v>
+        <v>MASTERCLASS</v>
       </c>
       <c r="F5" t="str">
-        <v>https://zoom.us/j/123456789</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
+        <v>https://meet.google.com/sales-roleplay</v>
+      </c>
+      <c r="G5" t="str">
+        <v>8</v>
       </c>
       <c r="H5" t="str">
-        <v>Basic grammar review session</v>
+        <v>Advanced sales roleplay with negotiation techniques and objection handling.</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>https://docs.google.com/document/d/negotiation-playbook, https://drive.google.com/file/d/roleplay-scripts, https://drive.google.com/file/d/vocabulary-list</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Business English</v>
-      </c>
-      <c r="B6" s="1" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="D6" s="1" t="str">
+        <v>Monthly Webinar: Career Tips</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C6" t="str">
         <v>17:00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>18:00</v>
       </c>
       <c r="E6" t="str">
         <v>WEBINAR</v>
       </c>
       <c r="F6" t="str">
-        <v>https://meet.google.com/aaa-bbbb-ccc</v>
+        <v>https://meet.google.com/webinar-career</v>
       </c>
       <c r="G6" t="str">
+        <v>50</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Monthly webinar on career development tips for English learners.</v>
+      </c>
+      <c r="I6" t="str">
         <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>Professional vocabulary and email writing</v>
-      </c>
-      <c r="I6" t="str">
-        <v>https://docs.google.com/presentation/d/business-slides</v>
       </c>
     </row>
   </sheetData>
@@ -753,46 +592,312 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="55.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Valid Class Types</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>REGULAR</v>
+        <v>📋 BULK UPLOAD CLASSES — Instructions</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WORKSHOP</v>
+        <v>COLUMNS</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>WEBINAR</v>
+        <v>Column</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Required</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Example</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>QA</v>
+        <v>Title</v>
+      </c>
+      <c r="B5" t="str">
+        <v>✅ Yes</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Name of the class session.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Business English Basics</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MASTERCLASS</v>
+        <v>Date</v>
+      </c>
+      <c r="B6" t="str">
+        <v>✅ Yes</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Class date. Supports: YYYY-MM-DD, DD-MM-YYYY, MM/DD/YYYY, or Excel serial dates. Only future dates allowed.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-07</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Start Time</v>
+      </c>
+      <c r="B7" t="str">
+        <v>✅ Yes</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Start time in HH:MM (24-hour format) or Excel time format.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>End Time</v>
+      </c>
+      <c r="B8" t="str">
+        <v>✅ Yes</v>
+      </c>
+      <c r="C8" t="str">
+        <v>End time in HH:MM (24-hour format) or Excel time format.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Class type. Must be one of: REGULAR, WORKSHOP, WEBINAR, QA, MASTERCLASS. Defaults to REGULAR if empty.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>WORKSHOP</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Meet Link</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Video call link (Google Meet, Zoom, etc.).</v>
+      </c>
+      <c r="D10" t="str">
+        <v>https://meet.google.com/abc-defg-hij</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Capacity</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Maximum number of students. Leave empty for unlimited.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Description</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Description of the class content and objectives.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Practice IELTS speaking Part 2 &amp; 3.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Materials Link</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Link(s) to class materials. For MULTIPLE materials, separate with commas. Students will see a selection modal to choose which material to open.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>https://drive.google.com/file1, https://drive.google.com/file2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ALTERNATIVE COLUMN NAMES (case-insensitive)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>The parser accepts these alternative names for flexibility:</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Title → titulo, class, nombre</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Date → fecha</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Start Time → start, starttime, hora inicio, inicio</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>End Time → end, endtime, hora fin, fin</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Type → tipo</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Meet Link → link, meetlink, meet, zoom, zoom link</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Capacity → capacidad, max, maxcapacity</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Description → descripcion, desc</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Materials Link → materials, materialslink, materiales</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SKILL BUILDER LIVE VISIBILITY</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>⚠️ This is NOT a column in the Excel file.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>After uploading and previewing the file, you will see a checkbox in the upload modal:</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">  ☑ Visible for Skill Builder Live — Makes ALL uploaded classes visible for Skill Builder Live plan users.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>This defaults to unchecked (not visible). The setting applies to ALL classes in the batch.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Note: Classes do not have a 'Visible for Skill Builder' option (only Skill Builder Live).</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>MULTIPLE MATERIALS LINKS</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>To provide multiple materials for a single class, separate the URLs with commas in the Materials Link column.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Example: https://drive.google.com/slides, https://drive.google.com/handout, https://www.loom.com/share/demo-video</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>When students view the class, they will see a modal allowing them to choose which material to open.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>LIMITS &amp; RULES</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>• Maximum 200 classes per upload batch.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>• Only future dates allowed (no past dates).</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>• Title, Date, Start Time and End Time are required for each row.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>• Supported file formats: .xlsx, .xls, .csv</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>• Times are treated as UTC. Make sure to account for timezone differences.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>• If Type is not provided or invalid, it defaults to REGULAR.</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>